--- a/AI_tasks_organized.xlsx
+++ b/AI_tasks_organized.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AI タスク一覧" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="カテゴリ別分類" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="手順書" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="要約" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AI タスク一覧" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="カテゴリ別分類" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="手順書" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,14 +32,32 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <color rgb="002E75B6"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -50,12 +70,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="13">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -64,7 +80,57 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BF8F00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C55A11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F7F7F"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,42 +140,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
+        <fgColor rgb="00595959"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00548235"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BF8F00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C55A11"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007F7F7F"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -188,92 +224,167 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -641,6 +752,420 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AI タスク 整理レポート</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Google Tasks「AI」リストから抽出・分類・手順化</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>■ 概要</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>対象タスクリスト</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Google Tasks「AI」リスト</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>総タスク数</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>33 件</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>分類カテゴリ数</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>5 カテゴリ</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>全件「未完了」</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>AIツール活用の整理・手順化・実行推進</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>■ カテゴリ別タスク数</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>カテゴリ</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>主なタスク</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Claude Code系</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>初期設定・コマンド・エージェント・セキュリティ・スキル</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>AI活用事例</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>価格比較・週レポート・日タスク・スライド作成</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>NotebookLM/Gemini系</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>プロンプト保管庫・Gem×LM連携・書籍管理・会議録</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Cowork/ツール系</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Cowork・Channels・Antigravity・ブラウザ操作・AI Studio</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>投資関連AIツール調査</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>■ 優先取り組み提案</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>内容・推奨理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>Claude Code 初期設定・基盤整備</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>code 初期設定 / .claude育てる / セキュリティ設定を先行して完了させ、開発基盤を確立する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>AI活用事例の実装（例1〜5）</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>具体的なアウトプットを出すことでAI活用の成果を可視化。週レポート・スライド自動化から着手推奨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>Coworkチーム導入</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>導入の注意事項を確認後、Channels設定・メンバー招待を実施。組織全体のAI活用推進につなげる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>NotebookLM プロンプト管理</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>プロンプト保管庫を整備し、Gem×LM連携を確立。ナレッジ管理の基盤として活用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Tasks→スプレッドシート自動化</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Google Tasksのデータをスプシに自動転記するフローを構築し、タスク管理を効率化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>■ 本ファイルの構成</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="3" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Sheet1: 要約</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>本シート。全体概要・カテゴリ集計・優先取り組み提案</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>Sheet2: AI タスク一覧</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>33件のタスクをカテゴリ色分けで一覧表示</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>Sheet3: カテゴリ別分類</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>5カテゴリに分けてタスクを整理</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>Sheet4: 手順書</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>カテゴリごとの概要・具体的な作業手順</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -653,769 +1178,769 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>タスク名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>改善 claude chrome</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="29" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="29" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E2" s="29" t="inlineStr"/>
+      <c r="F2" s="29" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>.claude 育てる</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
         <is>
           <t>Claude Code系</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
+      <c r="D3" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E3" s="30" t="inlineStr"/>
+      <c r="F3" s="30" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>code 活用事例28 KEITA</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Claude Code系</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr"/>
+      <c r="F4" s="30" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>code 初期設定</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>Claude Code系</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="D5" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E5" s="30" t="inlineStr"/>
+      <c r="F5" s="30" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>code コマンド早見表</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>Claude Code系</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr"/>
+      <c r="F6" s="30" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>code 堅めのセキュリティ</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>Claude Code系</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr"/>
+      <c r="F7" s="30" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>code 階層、フォルダ 公式</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Claude Code系</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr"/>
+      <c r="F8" s="30" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>code エージェントのつくりかた</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>Claude Code系</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="inlineStr"/>
+      <c r="F9" s="30" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>code skill</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>Claude Code系</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr"/>
+      <c r="F10" s="30" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>codeコンソール</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>Claude Code系</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E11" s="30" t="inlineStr"/>
+      <c r="F11" s="30" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Claude code</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>Claude Code系</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr"/>
+      <c r="F12" s="30" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>ニュース codeクラウド実行</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>Claude Code系</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E13" s="30" t="inlineStr"/>
+      <c r="F13" s="30" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>antigravity 日本語プロンプト</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>Cowork/ツール系</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr"/>
+      <c r="F14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>antigravity</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>Cowork/ツール系</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr"/>
+      <c r="F15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>ブラウザ操作</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>Cowork/ツール系</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="inlineStr"/>
+      <c r="F16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>拡張機能 PC変更</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>Cowork/ツール系</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr"/>
+      <c r="F17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>cowork 導入の注意</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="31" t="inlineStr">
         <is>
           <t>Cowork/ツール系</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr"/>
+      <c r="F18" s="31" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>cowork</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="31" t="inlineStr">
         <is>
           <t>Cowork/ツール系</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr"/>
+      <c r="F19" s="31" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>channels 設定</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="31" t="inlineStr">
         <is>
           <t>Cowork/ツール系</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr"/>
+      <c r="F20" s="31" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>google AI Studio</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="31" t="inlineStr">
         <is>
           <t>Cowork/ツール系</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr"/>
+      <c r="F21" s="31" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="31" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>Tasks →スプシ化</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="31" t="inlineStr">
         <is>
           <t>Cowork/ツール系</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr"/>
+      <c r="F22" s="31" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="32" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>meet文字起こしと構造化 Gemini？</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="32" t="inlineStr">
         <is>
           <t>NotebookLM/Gemini系</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr"/>
+      <c r="F23" s="32" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="31" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>skills人格設定</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="31" t="inlineStr">
         <is>
           <t>Cowork/ツール系</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr"/>
+      <c r="F24" s="31" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="29" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>投資</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="D25" s="29" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E25" s="29" t="inlineStr"/>
+      <c r="F25" s="29" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="32" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>notebookLM プロンプト保管庫</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="32" t="inlineStr">
         <is>
           <t>NotebookLM/Gemini系</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr"/>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E26" s="32" t="inlineStr"/>
+      <c r="F26" s="32" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="32" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>gem x LM すべて</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="32" t="inlineStr">
         <is>
           <t>NotebookLM/Gemini系</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr"/>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr"/>
+      <c r="F27" s="32" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="32" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>（書籍LM）</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="32" t="inlineStr">
         <is>
           <t>NotebookLM/Gemini系</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr"/>
+      <c r="F28" s="32" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="30" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>.claude フォルダ 説明</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>Claude Code系</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E29" s="30" t="inlineStr"/>
+      <c r="F29" s="30" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="33" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>例1 価格比較</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>AI活用事例</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr"/>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E30" s="33" t="inlineStr"/>
+      <c r="F30" s="33" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="33" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>例2 週レポート作成</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>AI活用事例</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E31" s="33" t="inlineStr"/>
+      <c r="F31" s="33" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="33" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>例3 日タスク作成→tasksからも？</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>AI活用事例</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E32" s="33" t="inlineStr"/>
+      <c r="F32" s="33" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>例4 スライド作成</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>AI活用事例</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E33" s="33" t="inlineStr"/>
+      <c r="F33" s="33" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="33" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>例5 ダサくないスライド</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="33" t="inlineStr">
         <is>
           <t>AI活用事例</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr"/>
-      <c r="F34" s="6" t="inlineStr"/>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="inlineStr"/>
+      <c r="F34" s="33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1432,755 +1957,755 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>■ Claude Code系（12件）</t>
         </is>
       </c>
-      <c r="B1" s="8" t="n"/>
-      <c r="C1" s="8" t="n"/>
-      <c r="D1" s="8" t="n"/>
-      <c r="E1" s="9" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>タスク名</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>.claude 育てる</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
+      <c r="C3" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D3" s="30" t="inlineStr"/>
+      <c r="E3" s="30" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>code 活用事例28 KEITA</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr"/>
+      <c r="E4" s="30" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>code 初期設定</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="inlineStr"/>
+      <c r="E5" s="30" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>code コマンド早見表</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr"/>
+      <c r="E6" s="30" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>code 堅めのセキュリティ</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr"/>
+      <c r="E7" s="30" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>code 階層、フォルダ 公式</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr"/>
+      <c r="E8" s="30" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>code エージェントのつくりかた</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr"/>
+      <c r="E9" s="30" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>code skill</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr"/>
+      <c r="E10" s="30" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>codeコンソール</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr"/>
+      <c r="E11" s="30" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Claude code</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr"/>
+      <c r="E12" s="30" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>ニュース codeクラウド実行</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr"/>
+      <c r="E13" s="30" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>.claude フォルダ 説明</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr"/>
+      <c r="E14" s="30" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>■ AI活用事例（5件）</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="9" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>タスク名</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>例1 価格比較</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="6" t="inlineStr"/>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr"/>
+      <c r="E18" s="33" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>例2 週レポート作成</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr"/>
+      <c r="E19" s="33" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>例3 日タスク作成→tasksからも？</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="inlineStr"/>
+      <c r="E20" s="33" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>例4 スライド作成</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr"/>
+      <c r="E21" s="33" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>例5 ダサくないスライド</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="6" t="inlineStr"/>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr"/>
+      <c r="E22" s="33" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>■ NotebookLM/Gemini系（4件）</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="9" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="38" t="inlineStr">
         <is>
           <t>タスク名</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="38" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="38" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="38" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>meet文字起こしと構造化 Gemini？</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr"/>
+      <c r="E26" s="32" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>notebookLM プロンプト保管庫</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr"/>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr"/>
+      <c r="E27" s="32" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>gem x LM すべて</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr"/>
+      <c r="E28" s="32" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>（書籍LM）</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr"/>
+      <c r="E29" s="32" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="39" t="inlineStr">
         <is>
           <t>■ Cowork/ツール系（10件）</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="9" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="40" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="40" t="inlineStr">
         <is>
           <t>タスク名</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="40" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="40" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E32" s="40" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="31" t="inlineStr">
         <is>
           <t>antigravity 日本語プロンプト</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr"/>
+      <c r="E33" s="31" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="31" t="inlineStr">
         <is>
           <t>antigravity</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="inlineStr"/>
+      <c r="E34" s="31" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>ブラウザ操作</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr"/>
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="inlineStr"/>
+      <c r="E35" s="31" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>拡張機能 PC変更</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr"/>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D36" s="31" t="inlineStr"/>
+      <c r="E36" s="31" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>cowork 導入の注意</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="inlineStr"/>
+      <c r="E37" s="31" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>cowork</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D38" s="31" t="inlineStr"/>
+      <c r="E38" s="31" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="31" t="inlineStr">
         <is>
           <t>channels 設定</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="inlineStr"/>
+      <c r="E39" s="31" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="31" t="inlineStr">
         <is>
           <t>google AI Studio</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr"/>
-      <c r="E40" s="4" t="inlineStr"/>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="inlineStr"/>
+      <c r="E40" s="31" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="31" t="inlineStr">
         <is>
           <t>Tasks →スプシ化</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr"/>
-      <c r="E41" s="4" t="inlineStr"/>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="inlineStr"/>
+      <c r="E41" s="31" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="31" t="inlineStr">
         <is>
           <t>skills人格設定</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr"/>
-      <c r="E42" s="4" t="inlineStr"/>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="inlineStr"/>
+      <c r="E42" s="31" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="41" t="inlineStr">
         <is>
           <t>■ その他（2件）</t>
         </is>
       </c>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="9" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B45" s="42" t="inlineStr">
         <is>
           <t>タスク名</t>
         </is>
       </c>
-      <c r="C45" s="17" t="inlineStr">
+      <c r="C45" s="42" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="D45" s="42" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E45" s="42" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="29" t="inlineStr">
         <is>
           <t>改善 claude chrome</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D46" s="29" t="inlineStr"/>
+      <c r="E46" s="29" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="29" t="inlineStr">
         <is>
           <t>投資</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>未完了</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>未完了</t>
+        </is>
+      </c>
+      <c r="D47" s="29" t="inlineStr"/>
+      <c r="E47" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2194,7 +2719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2209,705 +2734,705 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>AI タスク 手順書</t>
         </is>
       </c>
-      <c r="B1" s="8" t="n"/>
-      <c r="C1" s="9" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>【Claude Code系】</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="9" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>概要</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="9" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="3" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Claude Codeの導入・設定・活用に関するタスク群。開発環境の整備からスキル習得まで含む。</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="9" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="3" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>作業内容</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>詳細・備考</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>初期設定を完了する</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>code 初期設定 タスクを参照。認証・プロジェクト設定を行う。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>コマンド早見表を作成する</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>code コマンド早見表 タスク。よく使うコマンドを一覧化。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>フォルダ・階層構造を整理する</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>code 階層、フォルダ 公式 タスク。公式ドキュメントを参照。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>.claudeフォルダを育てる</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>.claude 育てる / .claude フォルダ 説明 タスク。カスタム設定を充実させる。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>セキュリティ設定を行う</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>code 堅めのセキュリティ タスク。アクセス制御・権限設定を確認。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="47" t="inlineStr">
         <is>
           <t>Skillsを設定する</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>code skill / skills人格設定 タスク。AIエージェントの役割を定義。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>エージェントの作り方を学ぶ</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>code エージェントのつくりかた タスク。公式ドキュメント・サンプルを学習。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="47" t="inlineStr">
         <is>
           <t>Chrome拡張・コンソールを整備</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>改善 claude chrome / codeコンソール タスク。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="47" t="inlineStr">
         <is>
           <t>活用事例28を整備 (KEITA)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>code 活用事例28 KEITA タスク。社内展開用の事例集を作成。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="47" t="inlineStr">
         <is>
           <t>クラウド実行環境を確認</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>ニュース codeクラウド実行 タスク。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="48" t="inlineStr">
         <is>
           <t>【AI活用事例】</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="9" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="45" t="inlineStr">
         <is>
           <t>概要</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="9" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="3" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>Claude Codeを活用した具体的な業務改善事例の整備。</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="9" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="3" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>作業内容</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>詳細・備考</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="49" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>例1: 価格比較を実装</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>AIを使った価格データの自動収集・比較スクリプト作成。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>例2: 週レポート作成を自動化</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>週次レポートの雛形生成・データ集計を自動化。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="49" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="49" t="inlineStr">
         <is>
           <t>例3: 日タスク作成を自動化</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>Google Tasksと連携した日次タスクの自動生成フローを構築。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="49" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>例4: スライド作成を効率化</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>AIによるプレゼン資料の自動生成・構成提案。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="49" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="49" t="inlineStr">
         <is>
           <t>例5: ダサくないスライドを作成</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>デザインテンプレート活用でビジュアルクオリティを向上。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="50" t="inlineStr">
         <is>
           <t>【NotebookLM/Gemini系】</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="9" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="45" t="inlineStr">
         <is>
           <t>概要</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="9" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="3" t="n"/>
     </row>
     <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="46" t="inlineStr">
         <is>
           <t>NotebookLM・Geminiを活用した情報管理・分析タスク。</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="9" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="3" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>作業内容</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="38" t="inlineStr">
         <is>
           <t>詳細・備考</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="51" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="51" t="inlineStr">
         <is>
           <t>NotebookLMのプロンプト保管庫を整備</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="32" t="inlineStr">
         <is>
           <t>notebookLM プロンプト保管庫 タスク。よく使うプロンプトを体系化して保存。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="51" t="inlineStr">
         <is>
           <t>Gem × LM の連携設定</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="32" t="inlineStr">
         <is>
           <t>gem x LM すべて タスク。GeminiとNotebookLMの連携フローを確立。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="51" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="B33" s="51" t="inlineStr">
         <is>
           <t>書籍LMを整備</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="32" t="inlineStr">
         <is>
           <t>（書籍LM）タスク。書籍情報のNotebookLM管理を設定。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="51" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="51" t="inlineStr">
         <is>
           <t>Meetの文字起こし・構造化</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="32" t="inlineStr">
         <is>
           <t>meet文字起こしと構造化 Gemini？タスク。会議録の自動構造化フローを構築。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="52" t="inlineStr">
         <is>
           <t>【Cowork/ツール系】</t>
         </is>
       </c>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="9" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="45" t="inlineStr">
         <is>
           <t>概要</t>
         </is>
       </c>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="9" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="3" t="n"/>
     </row>
     <row r="38" ht="40" customHeight="1">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="46" t="inlineStr">
         <is>
           <t>Cowork・Antigravity等のAIツールの導入・設定タスク。</t>
         </is>
       </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="9" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="3" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="40" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>作業内容</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C39" s="40" t="inlineStr">
         <is>
           <t>詳細・備考</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="28" t="inlineStr">
+      <c r="A40" s="53" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B40" s="28" t="inlineStr">
+      <c r="B40" s="53" t="inlineStr">
         <is>
           <t>Cowork導入時の注意事項を確認</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="31" t="inlineStr">
         <is>
           <t>cowork 導入の注意 タスク。契約・権限・データ管理ポリシーを確認。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="28" t="inlineStr">
+      <c r="A41" s="53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B41" s="28" t="inlineStr">
+      <c r="B41" s="53" t="inlineStr">
         <is>
           <t>Coworkを設定・運用開始</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="31" t="inlineStr">
         <is>
           <t>cowork タスク。チームアカウントの設定・メンバー招待を実施。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="28" t="inlineStr">
+      <c r="A42" s="53" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B42" s="28" t="inlineStr">
+      <c r="B42" s="53" t="inlineStr">
         <is>
           <t>Channelsを設定</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="31" t="inlineStr">
         <is>
           <t>channels 設定 タスク。通知・連携チャンネルを整備。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="28" t="inlineStr">
+      <c r="A43" s="53" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B43" s="28" t="inlineStr">
+      <c r="B43" s="53" t="inlineStr">
         <is>
           <t>Antigravityの日本語プロンプトを整備</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="31" t="inlineStr">
         <is>
           <t>antigravity / antigravity 日本語プロンプト タスク。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="28" t="inlineStr">
+      <c r="A44" s="53" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B44" s="28" t="inlineStr">
+      <c r="B44" s="53" t="inlineStr">
         <is>
           <t>ブラウザ操作自動化を設定</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="31" t="inlineStr">
         <is>
           <t>ブラウザ操作 タスク。AIによるブラウザ自動化ツールを導入。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="28" t="inlineStr">
+      <c r="A45" s="53" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B45" s="28" t="inlineStr">
+      <c r="B45" s="53" t="inlineStr">
         <is>
           <t>PC変更時の拡張機能を引き継ぎ</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="31" t="inlineStr">
         <is>
           <t>拡張機能 PC変更 タスク。Chrome拡張の設定をエクスポート・インポート。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="28" t="inlineStr">
+      <c r="A46" s="53" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B46" s="28" t="inlineStr">
+      <c r="B46" s="53" t="inlineStr">
         <is>
           <t>Google AI Studioを活用</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="31" t="inlineStr">
         <is>
           <t>google AI Studio タスク。APIキー取得・プロトタイプ開発環境として活用。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="28" t="inlineStr">
+      <c r="A47" s="53" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B47" s="28" t="inlineStr">
+      <c r="B47" s="53" t="inlineStr">
         <is>
           <t>TasksのスプレッドシートB化</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="31" t="inlineStr">
         <is>
           <t>Tasks →スプシ化 タスク。Google Tasksデータを自動でスプシに転記。</t>
         </is>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="A49" s="54" t="inlineStr">
         <is>
           <t>【その他】</t>
         </is>
       </c>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="9" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="inlineStr">
+      <c r="A50" s="45" t="inlineStr">
         <is>
           <t>概要</t>
         </is>
       </c>
-      <c r="B50" s="8" t="n"/>
-      <c r="C50" s="9" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="3" t="n"/>
     </row>
     <row r="51" ht="40" customHeight="1">
-      <c r="A51" s="21" t="inlineStr">
+      <c r="A51" s="46" t="inlineStr">
         <is>
           <t>上記カテゴリに分類されないAI関連タスク。</t>
         </is>
       </c>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="9" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="3" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="42" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B52" s="17" t="inlineStr">
+      <c r="B52" s="42" t="inlineStr">
         <is>
           <t>作業内容</t>
         </is>
       </c>
-      <c r="C52" s="17" t="inlineStr">
+      <c r="C52" s="42" t="inlineStr">
         <is>
           <t>詳細・備考</t>
         </is>
       </c>
     </row>
     <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="30" t="inlineStr">
+      <c r="A53" s="55" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B53" s="30" t="inlineStr">
+      <c r="B53" s="55" t="inlineStr">
         <is>
           <t>投資関連AIツールを調査</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="29" t="inlineStr">
         <is>
           <t>投資 タスク。AIを活用した投資分析・情報収集ツールを調査・導入。</t>
         </is>
